--- a/artfynd/A 33691-2024 artfynd.xlsx
+++ b/artfynd/A 33691-2024 artfynd.xlsx
@@ -2356,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536820</v>
+        <v>119536818</v>
       </c>
       <c r="B17" t="n">
         <v>90580</v>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661622</v>
+        <v>661621</v>
       </c>
       <c r="R17" t="n">
-        <v>7175497</v>
+        <v>7175822</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536818</v>
+        <v>119536820</v>
       </c>
       <c r="B18" t="n">
         <v>90580</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>661621</v>
+        <v>661622</v>
       </c>
       <c r="R18" t="n">
-        <v>7175822</v>
+        <v>7175497</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33691-2024 artfynd.xlsx
+++ b/artfynd/A 33691-2024 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536673</v>
+        <v>119536819</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661602</v>
+        <v>661637</v>
       </c>
       <c r="R8" t="n">
-        <v>7175804</v>
+        <v>7175720</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536112</v>
+        <v>119537141</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>79642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,42 +1468,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kronoborg, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661622</v>
+        <v>661600</v>
       </c>
       <c r="R9" t="n">
-        <v>7175822</v>
+        <v>7175800</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536398</v>
+        <v>119536112</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,34 +1584,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kronoborg, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661538</v>
+        <v>661622</v>
       </c>
       <c r="R10" t="n">
-        <v>7175805</v>
+        <v>7175822</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537141</v>
+        <v>119536398</v>
       </c>
       <c r="B13" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661600</v>
+        <v>661538</v>
       </c>
       <c r="R13" t="n">
-        <v>7175800</v>
+        <v>7175805</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536819</v>
+        <v>119536818</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661637</v>
+        <v>661621</v>
       </c>
       <c r="R14" t="n">
-        <v>7175720</v>
+        <v>7175822</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537025</v>
+        <v>119536673</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661673</v>
+        <v>661602</v>
       </c>
       <c r="R16" t="n">
-        <v>7175592</v>
+        <v>7175804</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536818</v>
+        <v>119537025</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,21 +2372,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661621</v>
+        <v>661673</v>
       </c>
       <c r="R17" t="n">
-        <v>7175822</v>
+        <v>7175592</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33691-2024 artfynd.xlsx
+++ b/artfynd/A 33691-2024 artfynd.xlsx
@@ -2244,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536673</v>
+        <v>119537025</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661602</v>
+        <v>661673</v>
       </c>
       <c r="R16" t="n">
-        <v>7175804</v>
+        <v>7175592</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537025</v>
+        <v>119536673</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,21 +2372,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661673</v>
+        <v>661602</v>
       </c>
       <c r="R17" t="n">
-        <v>7175592</v>
+        <v>7175804</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33691-2024 artfynd.xlsx
+++ b/artfynd/A 33691-2024 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536819</v>
+        <v>119536112</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,34 +1360,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kronoborg, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661637</v>
+        <v>661622</v>
       </c>
       <c r="R8" t="n">
-        <v>7175720</v>
+        <v>7175822</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1419,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537141</v>
+        <v>119536398</v>
       </c>
       <c r="B9" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,25 +1472,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661600</v>
+        <v>661538</v>
       </c>
       <c r="R9" t="n">
-        <v>7175800</v>
+        <v>7175805</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536112</v>
+        <v>119536818</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,35 +1588,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kronoborg, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661622</v>
+        <v>661621</v>
       </c>
       <c r="R10" t="n">
         <v>7175822</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536674</v>
+        <v>119536672</v>
       </c>
       <c r="B11" t="n">
         <v>79607</v>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661673</v>
+        <v>661589</v>
       </c>
       <c r="R11" t="n">
-        <v>7175591</v>
+        <v>7175833</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1796,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536671</v>
+        <v>119536674</v>
       </c>
       <c r="B12" t="n">
         <v>79607</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661539</v>
+        <v>661673</v>
       </c>
       <c r="R12" t="n">
-        <v>7175804</v>
+        <v>7175591</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536398</v>
+        <v>119537025</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661538</v>
+        <v>661673</v>
       </c>
       <c r="R13" t="n">
-        <v>7175805</v>
+        <v>7175592</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536818</v>
+        <v>119536673</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661621</v>
+        <v>661602</v>
       </c>
       <c r="R14" t="n">
-        <v>7175822</v>
+        <v>7175804</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536672</v>
+        <v>119536671</v>
       </c>
       <c r="B15" t="n">
         <v>79607</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661589</v>
+        <v>661539</v>
       </c>
       <c r="R15" t="n">
-        <v>7175833</v>
+        <v>7175804</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537025</v>
+        <v>119536820</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661673</v>
+        <v>661622</v>
       </c>
       <c r="R16" t="n">
-        <v>7175592</v>
+        <v>7175497</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536673</v>
+        <v>119536819</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,21 +2372,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661602</v>
+        <v>661637</v>
       </c>
       <c r="R17" t="n">
-        <v>7175804</v>
+        <v>7175720</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536820</v>
+        <v>119537141</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>79642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,25 +2480,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>661622</v>
+        <v>661600</v>
       </c>
       <c r="R18" t="n">
-        <v>7175497</v>
+        <v>7175800</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
